--- a/riscv-csr.xlsx
+++ b/riscv-csr.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://yongateknoloji-my.sharepoint.com/personal/huseyin_dinc_yongatek_com/Documents/work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\hd\riscv-simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{28A2EF63-AD92-4EC2-9889-B2B9CE036766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7EEBDFA-CA62-4ED0-A553-BE2FC35A6FCA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FE42BB-282B-41FC-A45A-529DFCA491D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="529" activeTab="1" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="529" activeTab="2" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR Table" sheetId="1" r:id="rId1"/>
-    <sheet name="mstatus" sheetId="2" r:id="rId2"/>
-    <sheet name="mstatush" sheetId="3" r:id="rId3"/>
+    <sheet name="mstatus mstatush" sheetId="2" r:id="rId2"/>
+    <sheet name="mip mie" sheetId="5" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="176">
   <si>
     <t>misa</t>
   </si>
@@ -193,13 +194,382 @@
     <t>12-11</t>
   </si>
   <si>
-    <t>11-10</t>
-  </si>
-  <si>
     <t>Index</t>
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>31-11</t>
+  </si>
+  <si>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>MDT</t>
+  </si>
+  <si>
+    <t>MPELP</t>
+  </si>
+  <si>
+    <t>MPV</t>
+  </si>
+  <si>
+    <t>GVA</t>
+  </si>
+  <si>
+    <t>MBE</t>
+  </si>
+  <si>
+    <t>SBE</t>
+  </si>
+  <si>
+    <t>Supervisor Interrupt Enable</t>
+  </si>
+  <si>
+    <t>Machine Interrupt Enable</t>
+  </si>
+  <si>
+    <t>Supervisor Previous Interrupt Enable</t>
+  </si>
+  <si>
+    <t>Machine Previous Interrupt Enable</t>
+  </si>
+  <si>
+    <t>Long Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Implemented</t>
+  </si>
+  <si>
+    <t>User Big Endian</t>
+  </si>
+  <si>
+    <t>Machine Big Endian</t>
+  </si>
+  <si>
+    <t>Supervisor Big Endian</t>
+  </si>
+  <si>
+    <t>Reserved.</t>
+  </si>
+  <si>
+    <t>Reads as zero; writes ignored.</t>
+  </si>
+  <si>
+    <t>Machine Disable Trap</t>
+  </si>
+  <si>
+    <t>WARL</t>
+  </si>
+  <si>
+    <t>Detects unexpected traps while handling an M-mode trap.</t>
+  </si>
+  <si>
+    <t>Machine Previous Expected Landing Pad</t>
+  </si>
+  <si>
+    <t>Saves previous Expected Landing Pad state on a trap to M-mode.</t>
+  </si>
+  <si>
+    <t>Machine Previous Virtualization Mode</t>
+  </si>
+  <si>
+    <t>Records whether virtualization mode was active before a trap to M-mode.</t>
+  </si>
+  <si>
+    <t>Relevant to H extension.</t>
+  </si>
+  <si>
+    <t>Guest Virtual Address</t>
+  </si>
+  <si>
+    <t>Selects endianness for M-mode explicit memory accesses.</t>
+  </si>
+  <si>
+    <t>May be read-only zero for little-endian-only implementations.</t>
+  </si>
+  <si>
+    <t>Selects endianness for S-mode memory accesses and supervisor page-table accesses.</t>
+  </si>
+  <si>
+    <t>State Dirty</t>
+  </si>
+  <si>
+    <t>Indicates whether FS, VS, or XS contains Dirty state.</t>
+  </si>
+  <si>
+    <t>Can be constant zero when those fields are always zero.</t>
+  </si>
+  <si>
+    <t>Supervisor Disable Trap</t>
+  </si>
+  <si>
+    <t>Detects unexpected traps while handling an S-mode trap.</t>
+  </si>
+  <si>
+    <t>Supervisor Previous Expected Landing Pad</t>
+  </si>
+  <si>
+    <t>Saves previous Expected Landing Pad state on a trap to S-mode.</t>
+  </si>
+  <si>
+    <t>Trap SRET</t>
+  </si>
+  <si>
+    <t>Used to intercept supervisor trap returns.</t>
+  </si>
+  <si>
+    <t>Timeout Wait</t>
+  </si>
+  <si>
+    <t>Trap Virtual Memory</t>
+  </si>
+  <si>
+    <t>Allows M-mode to intercept S-mode virtual-memory management.</t>
+  </si>
+  <si>
+    <t>Make Executable Readable</t>
+  </si>
+  <si>
+    <t>Allows loads from pages with X=1 even when R=0.</t>
+  </si>
+  <si>
+    <t>Only relevant when page-based virtual memory is active.</t>
+  </si>
+  <si>
+    <t>Supervisor User Memory access</t>
+  </si>
+  <si>
+    <t>Allows S-mode loads/stores to pages marked U=1.</t>
+  </si>
+  <si>
+    <t>Does not permit S-mode instruction fetches from U pages.</t>
+  </si>
+  <si>
+    <t>Modify Privilege</t>
+  </si>
+  <si>
+    <t>Makes M-mode data accesses use the privilege specified by MPP.</t>
+  </si>
+  <si>
+    <t>Does not affect instruction fetches.</t>
+  </si>
+  <si>
+    <t>Extension State</t>
+  </si>
+  <si>
+    <t>Summarizes state of additional user-mode extensions.</t>
+  </si>
+  <si>
+    <t>Read-only zero when no such extensions exist.</t>
+  </si>
+  <si>
+    <t>Floating-Point State</t>
+  </si>
+  <si>
+    <t>Tracks floating-point state: Off, Initial, Clean, or Dirty.</t>
+  </si>
+  <si>
+    <t>May be read-only zero without F extension.</t>
+  </si>
+  <si>
+    <t>Machine Previous Privilege</t>
+  </si>
+  <si>
+    <t>Records privilege mode before a trap to M-mode.</t>
+  </si>
+  <si>
+    <t>Vector State</t>
+  </si>
+  <si>
+    <t>Tracks vector state: Off, Initial, Clean, or Dirty.</t>
+  </si>
+  <si>
+    <t>May be read-only zero without V extension.</t>
+  </si>
+  <si>
+    <t>Supervisor Previous Privilege</t>
+  </si>
+  <si>
+    <t>Records whether execution was in U or S mode before a trap to S-mode.</t>
+  </si>
+  <si>
+    <t>Stores previous MIE value when taking an M-mode trap.</t>
+  </si>
+  <si>
+    <t>Selects endianness for U-mode explicit loads and stores.</t>
+  </si>
+  <si>
+    <t>Stores previous SIE value when taking an S-mode trap.</t>
+  </si>
+  <si>
+    <t>Global interrupt-enable bit for M-mode.</t>
+  </si>
+  <si>
+    <t>Global interrupt-enable bit for S-mode.</t>
+  </si>
+  <si>
+    <t>Defined by Smdbltrp. Reset value is 1 when extension is implemented.</t>
+  </si>
+  <si>
+    <t>Defined by Zicfilp.</t>
+  </si>
+  <si>
+    <t>Indicates that mtval contains a guest virtual address.</t>
+  </si>
+  <si>
+    <t>Defined by Ssdbltrp.</t>
+  </si>
+  <si>
+    <t>When 1, executing SRET in S-mode raises an illegal-instruction exception.</t>
+  </si>
+  <si>
+    <t>Controls whether WFI executed below M-mode may be forced to trap after a bounded time.</t>
+  </si>
+  <si>
+    <t>Useful for virtualizing/intercepting WFI.</t>
+  </si>
+  <si>
+    <t>When 1, S-mode accesses to satp and execution of SFENCE.VMA/SINVAL.VMA trap.</t>
+  </si>
+  <si>
+    <t>Used by MRET.</t>
+  </si>
+  <si>
+    <t>0=U, 1=S. Used by SRET.</t>
+  </si>
+  <si>
+    <t>Restored into MIE by MRET.</t>
+  </si>
+  <si>
+    <t>Restored into SIE by SRET.</t>
+  </si>
+  <si>
+    <t>Cleared on trap to M-mode and restored from MPIE by MRET.</t>
+  </si>
+  <si>
+    <t>Cleared on trap to S-mode and restored from SPIE by SRET.</t>
+  </si>
+  <si>
+    <t>10-9</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>31-14</t>
+  </si>
+  <si>
+    <t>LCOFI{P,E}</t>
+  </si>
+  <si>
+    <t>Local Counter Overflow Interrupt {Pending, Enable}</t>
+  </si>
+  <si>
+    <t>MEI{P,E}</t>
+  </si>
+  <si>
+    <t>SEI{P,E}</t>
+  </si>
+  <si>
+    <t>MTI{P,E}</t>
+  </si>
+  <si>
+    <t>STI{P,E}</t>
+  </si>
+  <si>
+    <t>MSI{P,E}</t>
+  </si>
+  <si>
+    <t>SSI{P,E}</t>
+  </si>
+  <si>
+    <t>Machine External Interrupt {Pending, Enable}</t>
+  </si>
+  <si>
+    <t>Supervisor External Interrupt {Pending, Enable}</t>
+  </si>
+  <si>
+    <t>Machine Timer Interrupt {Pending, Enable}</t>
+  </si>
+  <si>
+    <t>Supervisor Timer Interrupt {Pending, Enable}</t>
+  </si>
+  <si>
+    <t>Machine Software Interrupt {Pending, Enable}</t>
+  </si>
+  <si>
+    <t>Supervisor Software Interrupt {Pending, Enable}</t>
+  </si>
+  <si>
+    <t>local counter-overflow interrupts</t>
+  </si>
+  <si>
+    <t>machine external interrupts</t>
+  </si>
+  <si>
+    <t>supervisor external interrupts</t>
+  </si>
+  <si>
+    <t>machine timer interrupts</t>
+  </si>
+  <si>
+    <t>supervisor timer interrupts</t>
+  </si>
+  <si>
+    <t>machine software interrupts</t>
+  </si>
+  <si>
+    <t>supervisor software interrupts</t>
   </si>
 </sst>
 </file>
@@ -241,7 +611,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -264,11 +634,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -282,17 +689,48 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -850,277 +1288,1074 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5B37D6-208E-490B-BE10-76292AE97411}">
-  <dimension ref="B2:AI25"/>
+  <dimension ref="A2:H38"/>
   <sheetFormatPr defaultColWidth="6.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="2"/>
-    <col min="2" max="2" width="7.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="6.85546875" style="2"/>
+    <col min="1" max="1" width="9.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="83" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="64.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" style="6" customWidth="1"/>
+    <col min="9" max="16384" width="6.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:35" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B3" s="6">
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+      <c r="B4" s="5">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+      <c r="B5" s="5">
+        <v>9</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="5">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="5">
+        <v>7</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="5">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="5">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="5">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="9"/>
+      <c r="B11" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="5">
         <v>31</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B4" s="6" t="s">
+      <c r="D12" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B5" s="6">
+      <c r="F13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="5">
         <v>24</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B6" s="6">
+      <c r="D14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="6" t="s">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="5">
+        <v>23</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B7" s="6">
+      <c r="D15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
+      <c r="B16" s="5">
         <v>22</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B8" s="6">
+      <c r="D16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="8"/>
+      <c r="B17" s="5">
         <v>21</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B9" s="6">
+      <c r="D17" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="5">
         <v>20</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B10" s="6">
+      <c r="D18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="5">
         <v>19</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="11" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B11" s="6">
+      <c r="D19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="5">
         <v>18</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>34</v>
       </c>
+      <c r="D20" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="8"/>
+      <c r="B21" s="5">
+        <v>17</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+      <c r="B22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="5">
+        <v>8</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="5">
+        <v>7</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="8"/>
+      <c r="B28" s="5">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="8"/>
+      <c r="B29" s="5">
+        <v>5</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="8"/>
+      <c r="B30" s="5">
+        <v>4</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="8"/>
+      <c r="B31" s="5">
+        <v>3</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="8"/>
+      <c r="B32" s="5">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="8"/>
+      <c r="B33" s="5">
+        <v>1</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="5">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="A12:A34"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B3:H34">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$H3="-"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$H3="No"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>$H3="Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0314B82E-650C-4B99-A3AD-EA297374FD57}">
+  <dimension ref="B2:G17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="6"/>
+    <col min="2" max="2" width="13.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
-      <c r="V11" s="5"/>
-      <c r="W11" s="5"/>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
-      <c r="AA11" s="5"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="5"/>
-      <c r="AD11" s="5"/>
-      <c r="AE11" s="5"/>
-      <c r="AF11" s="5"/>
-      <c r="AG11" s="5"/>
-      <c r="AH11" s="5"/>
-      <c r="AI11" s="5"/>
-    </row>
-    <row r="12" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
-        <v>17</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
-      <c r="V12" s="5"/>
-      <c r="W12" s="5"/>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
-      <c r="AA12" s="5"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="5"/>
-      <c r="AD12" s="5"/>
-      <c r="AE12" s="5"/>
-      <c r="AF12" s="5"/>
-      <c r="AG12" s="5"/>
-      <c r="AH12" s="5"/>
-      <c r="AI12" s="5"/>
-    </row>
-    <row r="13" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="2:35" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="6">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="6">
-        <v>7</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="6">
-        <v>6</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="6">
-        <v>5</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="6">
-        <v>4</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B22" s="6">
-        <v>3</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="6">
-        <v>2</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="6">
-        <v>1</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="6">
-        <v>0</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>27</v>
-      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8127DF61-C03E-4D3E-A957-51C68EDE4DBC}">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400D1ED3-44A7-49E9-A961-E022D71E5837}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/riscv-csr.xlsx
+++ b/riscv-csr.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\hd\riscv-simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10FE42BB-282B-41FC-A45A-529DFCA491D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5032DF2-4D45-40F6-9479-32E91F85A79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="529" activeTab="2" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="435" activeTab="1" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR Table" sheetId="1" r:id="rId1"/>
-    <sheet name="mstatus mstatush" sheetId="2" r:id="rId2"/>
+    <sheet name="mstatus mstatush sstatus" sheetId="2" r:id="rId2"/>
     <sheet name="mip mie" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="6" r:id="rId4"/>
+    <sheet name="mideleg medeleg medelegh" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="211">
   <si>
     <t>misa</t>
   </si>
@@ -570,6 +570,111 @@
   </si>
   <si>
     <t>supervisor software interrupts</t>
+  </si>
+  <si>
+    <t>15-14</t>
+  </si>
+  <si>
+    <t>31-16</t>
+  </si>
+  <si>
+    <t>Reserved</t>
+  </si>
+  <si>
+    <t>Custom Use</t>
+  </si>
+  <si>
+    <t>Supervisor Software Interrupt</t>
+  </si>
+  <si>
+    <t>Machine Software Interrupt</t>
+  </si>
+  <si>
+    <t>Supervisor Timer Interrupt</t>
+  </si>
+  <si>
+    <t>Machine Timer Interrupt</t>
+  </si>
+  <si>
+    <t>Supervisor External Interrupt</t>
+  </si>
+  <si>
+    <t>Machine External Interrupt</t>
+  </si>
+  <si>
+    <t>Counter Overflow Interrupt</t>
+  </si>
+  <si>
+    <t>15-0</t>
+  </si>
+  <si>
+    <t>31-24</t>
+  </si>
+  <si>
+    <t>23-20</t>
+  </si>
+  <si>
+    <t>Hardware Error</t>
+  </si>
+  <si>
+    <t>Software Check</t>
+  </si>
+  <si>
+    <t>Double Trap</t>
+  </si>
+  <si>
+    <t>Store/AMO page fault</t>
+  </si>
+  <si>
+    <t>Load Page Fault</t>
+  </si>
+  <si>
+    <t>Instruction page fault</t>
+  </si>
+  <si>
+    <t>Environment call from m-mode</t>
+  </si>
+  <si>
+    <t>Environment call from s-mode</t>
+  </si>
+  <si>
+    <t>Environment call from u-mode</t>
+  </si>
+  <si>
+    <t>Store/AMO access fault</t>
+  </si>
+  <si>
+    <t>Instruction address misaligned</t>
+  </si>
+  <si>
+    <t>Instruction access fault</t>
+  </si>
+  <si>
+    <t>Illegal instruction</t>
+  </si>
+  <si>
+    <t>Breakpoint</t>
+  </si>
+  <si>
+    <t>Load Address Misaligned</t>
+  </si>
+  <si>
+    <t>Load Access Fault</t>
+  </si>
+  <si>
+    <t>Store/AMO address misaligned</t>
+  </si>
+  <si>
+    <t>medelegh</t>
+  </si>
+  <si>
+    <t>Writeable</t>
+  </si>
+  <si>
+    <t>Default Value</t>
+  </si>
+  <si>
+    <t>In sstatus</t>
   </si>
 </sst>
 </file>
@@ -591,7 +696,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,6 +712,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -675,7 +792,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -695,6 +812,33 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -702,6 +846,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1288,7 +1441,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5B37D6-208E-490B-BE10-76292AE97411}">
-  <dimension ref="A2:H38"/>
+  <dimension ref="A2:I53"/>
   <sheetFormatPr defaultColWidth="6.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="6" bestFit="1" customWidth="1"/>
@@ -1298,11 +1451,12 @@
     <col min="5" max="5" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="83" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="64.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="6.85546875" style="6"/>
+    <col min="8" max="8" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="6.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -1327,9 +1481,12 @@
       <c r="H2" s="5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="I2" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -1349,9 +1506,10 @@
       <c r="H3" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="17"/>
       <c r="B4" s="5">
         <v>10</v>
       </c>
@@ -1373,9 +1531,10 @@
       <c r="H4" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="17"/>
       <c r="B5" s="5">
         <v>9</v>
       </c>
@@ -1397,9 +1556,10 @@
       <c r="H5" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
       <c r="B6" s="5">
         <v>8</v>
       </c>
@@ -1417,9 +1577,10 @@
       <c r="H6" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="17"/>
       <c r="B7" s="5">
         <v>7</v>
       </c>
@@ -1441,9 +1602,10 @@
       <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
       <c r="B8" s="5">
         <v>6</v>
       </c>
@@ -1465,9 +1627,10 @@
       <c r="H8" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1489,9 +1652,10 @@
       <c r="H9" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="17"/>
       <c r="B10" s="5">
         <v>4</v>
       </c>
@@ -1513,9 +1677,10 @@
       <c r="H10" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="9"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
       <c r="B11" s="5" t="s">
         <v>53</v>
       </c>
@@ -1533,9 +1698,10 @@
       <c r="H11" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="5">
@@ -1559,9 +1725,12 @@
       <c r="H12" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
+      <c r="I12" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
       <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
@@ -1579,9 +1748,10 @@
       <c r="H13" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
       <c r="B14" s="5">
         <v>24</v>
       </c>
@@ -1603,9 +1773,12 @@
       <c r="H14" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
+      <c r="I14" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
       <c r="B15" s="5">
         <v>23</v>
       </c>
@@ -1627,9 +1800,12 @@
       <c r="H15" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
+      <c r="I15" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
       <c r="B16" s="5">
         <v>22</v>
       </c>
@@ -1651,9 +1827,12 @@
       <c r="H16" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
+      <c r="I16" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
       <c r="B17" s="5">
         <v>21</v>
       </c>
@@ -1675,9 +1854,12 @@
       <c r="H17" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
+      <c r="I17" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
       <c r="B18" s="5">
         <v>20</v>
       </c>
@@ -1699,9 +1881,12 @@
       <c r="H18" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
+      <c r="I18" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="19"/>
       <c r="B19" s="5">
         <v>19</v>
       </c>
@@ -1723,9 +1908,12 @@
       <c r="H19" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
+      <c r="I19" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="19"/>
       <c r="B20" s="5">
         <v>18</v>
       </c>
@@ -1747,9 +1935,12 @@
       <c r="H20" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
+      <c r="I20" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="19"/>
       <c r="B21" s="5">
         <v>17</v>
       </c>
@@ -1771,9 +1962,12 @@
       <c r="H21" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
+      <c r="I21" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
       <c r="B22" s="5" t="s">
         <v>47</v>
       </c>
@@ -1795,9 +1989,12 @@
       <c r="H22" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
+      <c r="I22" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="19"/>
       <c r="B23" s="5" t="s">
         <v>48</v>
       </c>
@@ -1819,9 +2016,12 @@
       <c r="H23" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
+      <c r="I23" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="19"/>
       <c r="B24" s="5" t="s">
         <v>49</v>
       </c>
@@ -1843,9 +2043,12 @@
       <c r="H24" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
+      <c r="I24" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
       <c r="B25" s="5" t="s">
         <v>138</v>
       </c>
@@ -1867,9 +2070,12 @@
       <c r="H25" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
+      <c r="I25" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="19"/>
       <c r="B26" s="5">
         <v>8</v>
       </c>
@@ -1891,9 +2097,12 @@
       <c r="H26" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
+      <c r="I26" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="19"/>
       <c r="B27" s="5">
         <v>7</v>
       </c>
@@ -1915,9 +2124,12 @@
       <c r="H27" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
+      <c r="I27" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="19"/>
       <c r="B28" s="5">
         <v>6</v>
       </c>
@@ -1939,9 +2151,12 @@
       <c r="H28" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
+      <c r="I28" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="19"/>
       <c r="B29" s="5">
         <v>5</v>
       </c>
@@ -1963,9 +2178,12 @@
       <c r="H29" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
+      <c r="I29" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="19"/>
       <c r="B30" s="5">
         <v>4</v>
       </c>
@@ -1983,9 +2201,10 @@
       <c r="H30" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="19"/>
       <c r="B31" s="5">
         <v>3</v>
       </c>
@@ -2007,9 +2226,12 @@
       <c r="H31" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
+      <c r="I31" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="19"/>
       <c r="B32" s="5">
         <v>2</v>
       </c>
@@ -2027,9 +2249,10 @@
       <c r="H32" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="19"/>
       <c r="B33" s="5">
         <v>1</v>
       </c>
@@ -2051,9 +2274,12 @@
       <c r="H33" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
+      <c r="I33" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="19"/>
       <c r="B34" s="5">
         <v>0</v>
       </c>
@@ -2071,8 +2297,198 @@
       <c r="H34" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="20"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="20"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="20"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="20"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="20"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="20"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="20"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="20"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="20"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="21"/>
+      <c r="D43" s="21"/>
+      <c r="E43" s="21"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="21"/>
+      <c r="H43" s="21"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="20"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="20"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="20"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="20"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="20"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+      <c r="F48" s="21"/>
+      <c r="G48" s="21"/>
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="20"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="20"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="20"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21"/>
+      <c r="E51" s="21"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="21"/>
+      <c r="H51" s="21"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="20"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="20"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:A11"/>
@@ -2130,224 +2546,224 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2356,9 +2772,578 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400D1ED3-44A7-49E9-A961-E022D71E5837}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A6:L30"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="2"/>
+    <col min="3" max="3" width="33.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="7" width="8.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H6" s="8"/>
+      <c r="I6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="1">
+        <v>13</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="H9" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="7">
+        <v>12</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="12"/>
+      <c r="B11" s="1">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="1">
+        <v>19</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="12"/>
+      <c r="B12" s="7">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="1">
+        <v>18</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="12"/>
+      <c r="B13" s="1">
+        <v>9</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="7">
+        <v>17</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K13" s="7">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="12"/>
+      <c r="B14" s="7">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="1">
+        <v>16</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="12"/>
+      <c r="B15" s="1">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="1">
+        <v>15</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="12"/>
+      <c r="B16" s="7">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D16" s="7">
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="7">
+        <v>14</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="12"/>
+      <c r="B17" s="1">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="1">
+        <v>13</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="12"/>
+      <c r="B18" s="7">
+        <v>4</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="1">
+        <v>12</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="1">
+        <v>11</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="12"/>
+      <c r="B20" s="7">
+        <v>2</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="7">
+        <v>10</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="K20" s="7">
+        <v>0</v>
+      </c>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="1">
+        <v>9</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="B22" s="7">
+        <v>0</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D22" s="7">
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="1">
+        <v>8</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K22" s="1">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H23" s="15"/>
+      <c r="I23" s="1">
+        <v>7</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H24" s="15"/>
+      <c r="I24" s="1">
+        <v>6</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H25" s="15"/>
+      <c r="I25" s="1">
+        <v>5</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H26" s="15"/>
+      <c r="I26" s="1">
+        <v>4</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H27" s="15"/>
+      <c r="I27" s="1">
+        <v>3</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H28" s="15"/>
+      <c r="I28" s="1">
+        <v>2</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H29" s="15"/>
+      <c r="I29" s="1">
+        <v>1</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H30" s="14"/>
+      <c r="I30" s="1">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:A22"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="H9:H30"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/riscv-csr.xlsx
+++ b/riscv-csr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\hd\riscv-simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5032DF2-4D45-40F6-9479-32E91F85A79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494C8C09-CBCC-446A-A7CB-055F19FD3AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="435" activeTab="1" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" activeTab="1" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR Table" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="mip mie" sheetId="5" r:id="rId3"/>
     <sheet name="mideleg medeleg medelegh" sheetId="6" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="bin2hex_32">_xlfn.LAMBDA(_xlpm.bin_str,    _xlfn.LET(     _xlpm.padded, RIGHT(REPT("0", 32) &amp; _xlpm.bin_str, 32),     _xlfn.CONCAT(       BIN2HEX(MID(_xlpm.padded, 1, 8), 2),       BIN2HEX(MID(_xlpm.padded, 9, 8), 2),       BIN2HEX(MID(_xlpm.padded, 17, 8), 2),       BIN2HEX(MID(_xlpm.padded, 25, 8), 2)     )   ) )</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -35,14 +38,56 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
+<python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
+  <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
+    <initialization>
+      <code xml:space="preserve">import numpy as np
+import pandas as pd
+import matplotlib.pyplot as plt
+import seaborn as sns
+import statsmodels as sm
+import excel
+import warnings
+warnings.simplefilter('ignore')
+excel.set_xl_scalar_conversion(excel.convert_to_scalar)
+excel.set_xl_array_conversion(excel.convert_to_dataframe)
+</code>
+    </initialization>
+  </environmentDefinition>
+</python>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="214">
   <si>
     <t>misa</t>
   </si>
@@ -675,13 +720,22 @@
   </si>
   <si>
     <t>In sstatus</t>
+  </si>
+  <si>
+    <t>Implementation Mask</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Implementation Mask Joined</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -694,6 +748,17 @@
       <color theme="1"/>
       <name val="Georgia Pro Cond"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
     </font>
   </fonts>
   <fills count="6">
@@ -792,7 +857,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -827,17 +892,8 @@
     <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -851,10 +907,31 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1441,22 +1518,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D5B37D6-208E-490B-BE10-76292AE97411}">
-  <dimension ref="A2:I53"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr defaultColWidth="6.85546875" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="83" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="64.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="6.85546875" style="6"/>
+    <col min="3" max="3" width="6.42578125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="83" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="64.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="6" customWidth="1"/>
+    <col min="11" max="11" width="25.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.5703125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" style="6"/>
+    <col min="14" max="14" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="38.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="6.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N1" s="23"/>
+    </row>
+    <row r="2" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
@@ -1464,1045 +1550,1189 @@
         <v>50</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="K2" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="L2" s="21" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="22">
+        <v>21</v>
+      </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I3" s="9"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="22" t="str">
+        <f>REPT(IF(I3="Yes",1,0),C3)</f>
+        <v>000000000000000000000</v>
+      </c>
+      <c r="L3" s="24" t="str" cm="1">
+        <f t="array" ref="L3">bin2hex_32(_xlfn.CONCAT(K3:K11))</f>
+        <v>00000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="14"/>
       <c r="B4" s="5">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="22">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+      <c r="I4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="K4" s="22" t="str">
+        <f t="shared" ref="K4:K34" si="0">REPT(IF(I4="Yes",1,0),C4)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="24"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
       <c r="B5" s="5">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="22">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="9"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+      <c r="I5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="K5" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L5" s="24"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
       <c r="B6" s="5">
         <v>8</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="22">
+        <v>1</v>
+      </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="5"/>
+      <c r="F6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I6" s="9"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L6" s="24"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
       <c r="B7" s="5">
         <v>7</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="22">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="9"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
+      <c r="I7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L7" s="24"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
       <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="22">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="H8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+      <c r="I8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="9"/>
+      <c r="K8" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="24"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
       <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="22">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="H9" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+      <c r="I9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="24"/>
+      <c r="O9" s="23"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="14"/>
       <c r="B10" s="5">
         <v>4</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="22">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="H10" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+      <c r="I10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="24"/>
+    </row>
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="5"/>
+      <c r="C11" s="22">
+        <v>4</v>
+      </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="5"/>
+      <c r="F11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="H11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="J11" s="9"/>
+      <c r="K11" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0000</v>
+      </c>
+      <c r="L11" s="24"/>
+      <c r="O11" s="25"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="5">
         <v>31</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="22">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="H12" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
+      <c r="K12" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="24" t="str" cm="1">
+        <f t="array" ref="L12">bin2hex_32(_xlfn.CONCAT(K12:K34))</f>
+        <v>007E19AA</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
       <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="22">
+        <v>6</v>
+      </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="5"/>
+      <c r="F13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="I13" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>000000</v>
+      </c>
+      <c r="L13" s="24"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
       <c r="B14" s="5">
         <v>24</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="22">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
+      <c r="K14" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="24"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
       <c r="B15" s="5">
         <v>23</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
+      <c r="K15" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="24"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
       <c r="B16" s="5">
         <v>22</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="22">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="I16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
+      <c r="J16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L16" s="24"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
       <c r="B17" s="5">
         <v>21</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="22">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="H17" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
+      <c r="J17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L17" s="24"/>
+      <c r="N17" s="23"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
       <c r="B18" s="5">
         <v>20</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="22">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="I18" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
+      <c r="J18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L18" s="24"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
       <c r="B19" s="5">
         <v>19</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="22">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="H19" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="J19" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
+      <c r="K19" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L19" s="24"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
       <c r="B20" s="5">
         <v>18</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="22">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="H20" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="I20" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="J20" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
+      <c r="K20" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L20" s="24"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
       <c r="B21" s="5">
         <v>17</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="22">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="H21" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="I21" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="J21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L21" s="24"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
       <c r="B22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="22">
+        <v>2</v>
+      </c>
+      <c r="D22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
+      <c r="K22" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>00</v>
+      </c>
+      <c r="L22" s="24"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
       <c r="B23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="22">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="H23" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
+      <c r="K23" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>00</v>
+      </c>
+      <c r="L23" s="24"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
       <c r="B24" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="22">
+        <v>2</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="H24" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="I24" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
+      <c r="J24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
       <c r="B25" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="22">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="H25" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J25" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
+      <c r="K25" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>00</v>
+      </c>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
       <c r="B26" s="5">
         <v>8</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="22">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="H26" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="I26" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="J26" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
+      <c r="K26" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
       <c r="B27" s="5">
         <v>7</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="22">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="I27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
+      <c r="J27" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="22" t="str">
+        <f>REPT(IF(I27="Yes",1,0),C27)</f>
+        <v>1</v>
+      </c>
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
       <c r="B28" s="5">
         <v>6</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="22">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="E28" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
+      <c r="K28" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="24"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
       <c r="B29" s="5">
         <v>5</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="22">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="J29" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
+      <c r="K29" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L29" s="24"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="16"/>
       <c r="B30" s="5">
         <v>4</v>
       </c>
-      <c r="C30" s="5"/>
+      <c r="C30" s="22">
+        <v>1</v>
+      </c>
       <c r="D30" s="5"/>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="5"/>
+      <c r="F30" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="I30" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I30" s="9"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L30" s="24"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="16"/>
       <c r="B31" s="5">
         <v>3</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="22">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
+      <c r="J31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="16"/>
       <c r="B32" s="5">
         <v>2</v>
       </c>
-      <c r="C32" s="5"/>
+      <c r="C32" s="22">
+        <v>1</v>
+      </c>
       <c r="D32" s="5"/>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="5"/>
+      <c r="F32" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="H32" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="I32" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I32" s="9"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="16"/>
       <c r="B33" s="5">
         <v>1</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="22">
+        <v>1</v>
+      </c>
+      <c r="D33" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="I33" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="J33" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
+      <c r="K33" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L33" s="24"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="16"/>
       <c r="B34" s="5">
         <v>0</v>
       </c>
-      <c r="C34" s="5"/>
+      <c r="C34" s="22">
+        <v>1</v>
+      </c>
       <c r="D34" s="5"/>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="5"/>
+      <c r="F34" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="H34" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="I34" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="20"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="20"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="20"/>
-      <c r="B37" s="21"/>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="21"/>
-      <c r="H37" s="21"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="20"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="20"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="20"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="20"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="20"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="20"/>
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="20"/>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="20"/>
-      <c r="B45" s="21"/>
-      <c r="C45" s="21"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="20"/>
-      <c r="B46" s="21"/>
-      <c r="C46" s="21"/>
-      <c r="D46" s="21"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="21"/>
-      <c r="G46" s="21"/>
-      <c r="H46" s="21"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="20"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="20"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="20"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="20"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="20"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="20"/>
-      <c r="B52" s="21"/>
-      <c r="C52" s="21"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="20"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="24"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="12"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="12"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="12"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="12"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="12"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="12"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="12"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="12"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="12"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="12"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="12"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="12"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="12"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A3:A11"/>
     <mergeCell ref="A12:A34"/>
+    <mergeCell ref="L3:L11"/>
+    <mergeCell ref="L12:L34"/>
   </mergeCells>
-  <conditionalFormatting sqref="B3:H34">
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="B3:I34">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>$H3="-"</formula>
+      <formula>$I3="-"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$H3="No"</formula>
+      <formula>$I3="No"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>$H3="Yes"</formula>
+      <formula>$I3="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2817,7 +3047,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="17" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -2832,7 +3062,7 @@
       <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="18" t="s">
         <v>207</v>
       </c>
       <c r="I7" s="7" t="s">
@@ -2849,7 +3079,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="7" t="s">
         <v>176</v>
       </c>
@@ -2862,7 +3092,7 @@
       <c r="E8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="14"/>
+      <c r="H8" s="19"/>
       <c r="I8" s="7" t="s">
         <v>187</v>
       </c>
@@ -2877,7 +3107,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="1">
         <v>13</v>
       </c>
@@ -2888,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="18" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
@@ -2905,7 +3135,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="7">
         <v>12</v>
       </c>
@@ -2918,7 +3148,7 @@
       <c r="E10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="15"/>
+      <c r="H10" s="20"/>
       <c r="I10" s="7" t="s">
         <v>189</v>
       </c>
@@ -2933,7 +3163,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="1">
         <v>11</v>
       </c>
@@ -2944,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="H11" s="15"/>
+      <c r="H11" s="20"/>
       <c r="I11" s="1">
         <v>19</v>
       </c>
@@ -2959,7 +3189,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="7">
         <v>10</v>
       </c>
@@ -2972,7 +3202,7 @@
       <c r="E12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="15"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="1">
         <v>18</v>
       </c>
@@ -2985,7 +3215,7 @@
       <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -2996,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="H13" s="15"/>
+      <c r="H13" s="20"/>
       <c r="I13" s="7">
         <v>17</v>
       </c>
@@ -3009,7 +3239,7 @@
       <c r="L13" s="7"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="7">
         <v>8</v>
       </c>
@@ -3022,7 +3252,7 @@
       <c r="E14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="15"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="1">
         <v>16</v>
       </c>
@@ -3035,7 +3265,7 @@
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="1">
         <v>7</v>
       </c>
@@ -3046,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="H15" s="15"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="1">
         <v>15</v>
       </c>
@@ -3059,7 +3289,7 @@
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="7">
         <v>6</v>
       </c>
@@ -3072,7 +3302,7 @@
       <c r="E16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="15"/>
+      <c r="H16" s="20"/>
       <c r="I16" s="7">
         <v>14</v>
       </c>
@@ -3085,7 +3315,7 @@
       <c r="L16" s="7"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="1">
         <v>5</v>
       </c>
@@ -3096,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="H17" s="15"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="1">
         <v>13</v>
       </c>
@@ -3109,7 +3339,7 @@
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="7">
         <v>4</v>
       </c>
@@ -3122,7 +3352,7 @@
       <c r="E18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="15"/>
+      <c r="H18" s="20"/>
       <c r="I18" s="1">
         <v>12</v>
       </c>
@@ -3135,7 +3365,7 @@
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="12"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="1">
         <v>3</v>
       </c>
@@ -3146,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="H19" s="15"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="1">
         <v>11</v>
       </c>
@@ -3159,7 +3389,7 @@
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="12"/>
+      <c r="A20" s="17"/>
       <c r="B20" s="7">
         <v>2</v>
       </c>
@@ -3172,7 +3402,7 @@
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="15"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="7">
         <v>10</v>
       </c>
@@ -3185,7 +3415,7 @@
       <c r="L20" s="7"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="1">
         <v>1</v>
       </c>
@@ -3196,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="H21" s="15"/>
+      <c r="H21" s="20"/>
       <c r="I21" s="1">
         <v>9</v>
       </c>
@@ -3209,7 +3439,7 @@
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="7">
         <v>0</v>
       </c>
@@ -3222,7 +3452,7 @@
       <c r="E22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="15"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="1">
         <v>8</v>
       </c>
@@ -3235,7 +3465,7 @@
       <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H23" s="15"/>
+      <c r="H23" s="20"/>
       <c r="I23" s="1">
         <v>7</v>
       </c>
@@ -3248,7 +3478,7 @@
       <c r="L23" s="1"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H24" s="15"/>
+      <c r="H24" s="20"/>
       <c r="I24" s="1">
         <v>6</v>
       </c>
@@ -3261,7 +3491,7 @@
       <c r="L24" s="1"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H25" s="15"/>
+      <c r="H25" s="20"/>
       <c r="I25" s="1">
         <v>5</v>
       </c>
@@ -3274,7 +3504,7 @@
       <c r="L25" s="1"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H26" s="15"/>
+      <c r="H26" s="20"/>
       <c r="I26" s="1">
         <v>4</v>
       </c>
@@ -3287,7 +3517,7 @@
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H27" s="15"/>
+      <c r="H27" s="20"/>
       <c r="I27" s="1">
         <v>3</v>
       </c>
@@ -3300,7 +3530,7 @@
       <c r="L27" s="1"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H28" s="15"/>
+      <c r="H28" s="20"/>
       <c r="I28" s="1">
         <v>2</v>
       </c>
@@ -3313,7 +3543,7 @@
       <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H29" s="15"/>
+      <c r="H29" s="20"/>
       <c r="I29" s="1">
         <v>1</v>
       </c>
@@ -3326,7 +3556,7 @@
       <c r="L29" s="1"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H30" s="14"/>
+      <c r="H30" s="19"/>
       <c r="I30" s="1">
         <v>0</v>
       </c>

--- a/riscv-csr.xlsx
+++ b/riscv-csr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\hd\riscv-simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494C8C09-CBCC-446A-A7CB-055F19FD3AD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBAB5EA-141A-4DFE-9315-FE23E921BD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" activeTab="1" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="464" activeTab="1" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR Table" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="216">
   <si>
     <t>misa</t>
   </si>
@@ -729,6 +729,12 @@
   </si>
   <si>
     <t>Implementation Mask Joined</t>
+  </si>
+  <si>
+    <t>Implementation Mask sstatus</t>
+  </si>
+  <si>
+    <t>Implementation Mask sstatus joined</t>
   </si>
 </sst>
 </file>
@@ -857,7 +863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -895,6 +901,12 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -919,19 +931,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1533,14 +1545,14 @@
     <col min="10" max="10" width="11.42578125" style="6" customWidth="1"/>
     <col min="11" max="11" width="25.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="25.5703125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" style="6"/>
-    <col min="14" max="14" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32" style="6" customWidth="1"/>
     <col min="15" max="15" width="38.5703125" style="6" bestFit="1" customWidth="1"/>
     <col min="16" max="16384" width="6.85546875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N1" s="23"/>
+      <c r="N1" s="2"/>
     </row>
     <row r="2" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -1573,21 +1585,27 @@
       <c r="J2" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="13" t="s">
         <v>213</v>
       </c>
+      <c r="M2" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="1">
         <v>21</v>
       </c>
       <c r="D3" s="5"/>
@@ -1605,21 +1623,25 @@
         <v>139</v>
       </c>
       <c r="J3" s="9"/>
-      <c r="K3" s="22" t="str">
+      <c r="K3" s="1" t="str">
         <f>REPT(IF(I3="Yes",1,0),C3)</f>
         <v>000000000000000000000</v>
       </c>
-      <c r="L3" s="24" t="str" cm="1">
+      <c r="L3" s="19" t="str" cm="1">
         <f t="array" ref="L3">bin2hex_32(_xlfn.CONCAT(K3:K11))</f>
         <v>00000000</v>
       </c>
+      <c r="M3" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N3" s="24"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="5">
         <v>10</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -1641,18 +1663,22 @@
         <v>23</v>
       </c>
       <c r="J4" s="9"/>
-      <c r="K4" s="22" t="str">
+      <c r="K4" s="1" t="str">
         <f t="shared" ref="K4:K34" si="0">REPT(IF(I4="Yes",1,0),C4)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="24"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="5">
         <v>9</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1674,18 +1700,22 @@
         <v>23</v>
       </c>
       <c r="J5" s="9"/>
-      <c r="K5" s="22" t="str">
+      <c r="K5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L5" s="24"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N5" s="24"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="5">
         <v>8</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="5"/>
@@ -1703,18 +1733,22 @@
         <v>139</v>
       </c>
       <c r="J6" s="9"/>
-      <c r="K6" s="22" t="str">
+      <c r="K6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="24"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N6" s="24"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="5">
         <v>7</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1736,18 +1770,22 @@
         <v>23</v>
       </c>
       <c r="J7" s="9"/>
-      <c r="K7" s="22" t="str">
+      <c r="K7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="24"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N7" s="24"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -1769,18 +1807,22 @@
         <v>23</v>
       </c>
       <c r="J8" s="9"/>
-      <c r="K8" s="22" t="str">
+      <c r="K8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L8" s="24"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N8" s="24"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="5">
         <v>5</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="1">
         <v>1</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1802,19 +1844,23 @@
         <v>23</v>
       </c>
       <c r="J9" s="9"/>
-      <c r="K9" s="22" t="str">
+      <c r="K9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L9" s="24"/>
-      <c r="O9" s="23"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N9" s="24"/>
+      <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="5">
         <v>4</v>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="1">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1836,18 +1882,22 @@
         <v>23</v>
       </c>
       <c r="J10" s="9"/>
-      <c r="K10" s="22" t="str">
+      <c r="K10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="24"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N10" s="24"/>
     </row>
     <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="1">
         <v>4</v>
       </c>
       <c r="D11" s="5"/>
@@ -1865,21 +1915,25 @@
         <v>139</v>
       </c>
       <c r="J11" s="9"/>
-      <c r="K11" s="22" t="str">
+      <c r="K11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0000</v>
       </c>
-      <c r="L11" s="24"/>
-      <c r="O11" s="25"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="N11" s="24"/>
+      <c r="O11" s="14"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="18" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="5">
         <v>31</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1903,21 +1957,29 @@
       <c r="J12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K12" s="22" t="str">
+      <c r="K12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="24" t="str" cm="1">
+      <c r="L12" s="19" t="str" cm="1">
         <f t="array" ref="L12">bin2hex_32(_xlfn.CONCAT(K12:K34))</f>
         <v>007E19AA</v>
       </c>
+      <c r="M12" s="23" t="str">
+        <f>REPT(IF(AND(J12="Yes",I12="Yes"),1,0),C12)</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="25" t="str" cm="1">
+        <f t="array" ref="N12">bin2hex_32(_xlfn.CONCAT(M12:M34))</f>
+        <v>000C0122</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
+      <c r="A13" s="18"/>
       <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="1">
         <v>6</v>
       </c>
       <c r="D13" s="5"/>
@@ -1935,18 +1997,23 @@
         <v>139</v>
       </c>
       <c r="J13" s="9"/>
-      <c r="K13" s="22" t="str">
+      <c r="K13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>000000</v>
       </c>
-      <c r="L13" s="24"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="23" t="str">
+        <f t="shared" ref="M13:M34" si="1">REPT(IF(AND(J13="Yes",I13="Yes"),1,0),C13)</f>
+        <v>000000</v>
+      </c>
+      <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
+      <c r="A14" s="18"/>
       <c r="B14" s="5">
         <v>24</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="1">
         <v>1</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -1970,18 +2037,23 @@
       <c r="J14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="22" t="str">
+      <c r="K14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="24"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N14" s="26"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="5">
         <v>23</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="1">
         <v>1</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -2005,18 +2077,23 @@
       <c r="J15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K15" s="22" t="str">
+      <c r="K15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L15" s="24"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
+      <c r="A16" s="18"/>
       <c r="B16" s="5">
         <v>22</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="1">
         <v>1</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -2040,18 +2117,23 @@
       <c r="J16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="22" t="str">
+      <c r="K16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L16" s="24"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
+      <c r="A17" s="18"/>
       <c r="B17" s="5">
         <v>21</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="1">
         <v>1</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -2075,19 +2157,23 @@
       <c r="J17" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="22" t="str">
+      <c r="K17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L17" s="24"/>
-      <c r="N17" s="23"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N17" s="26"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="5">
         <v>20</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="1">
         <v>1</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -2111,18 +2197,23 @@
       <c r="J18" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="22" t="str">
+      <c r="K18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L18" s="24"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="26"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
+      <c r="A19" s="18"/>
       <c r="B19" s="5">
         <v>19</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="1">
         <v>1</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -2146,18 +2237,23 @@
       <c r="J19" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="22" t="str">
+      <c r="K19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L19" s="24"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N19" s="26"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="5">
         <v>18</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="1">
         <v>1</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -2181,18 +2277,23 @@
       <c r="J20" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K20" s="22" t="str">
+      <c r="K20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L20" s="24"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N20" s="26"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="5">
         <v>17</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -2216,18 +2317,23 @@
       <c r="J21" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="22" t="str">
+      <c r="K21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L21" s="24"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="26"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
+      <c r="A22" s="18"/>
       <c r="B22" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="1">
         <v>2</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -2251,18 +2357,23 @@
       <c r="J22" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="22" t="str">
+      <c r="K22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L22" s="24"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>00</v>
+      </c>
+      <c r="N22" s="26"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
+      <c r="A23" s="18"/>
       <c r="B23" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="1">
         <v>2</v>
       </c>
       <c r="D23" s="5" t="s">
@@ -2286,18 +2397,23 @@
       <c r="J23" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K23" s="22" t="str">
+      <c r="K23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L23" s="24"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>00</v>
+      </c>
+      <c r="N23" s="26"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="1">
         <v>2</v>
       </c>
       <c r="D24" s="5" t="s">
@@ -2321,18 +2437,23 @@
       <c r="J24" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K24" s="22" t="str">
+      <c r="K24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="L24" s="24"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>00</v>
+      </c>
+      <c r="N24" s="26"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
+      <c r="A25" s="18"/>
       <c r="B25" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="5" t="s">
@@ -2356,18 +2477,23 @@
       <c r="J25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="22" t="str">
+      <c r="K25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L25" s="24"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>00</v>
+      </c>
+      <c r="N25" s="26"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
+      <c r="A26" s="18"/>
       <c r="B26" s="5">
         <v>8</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="1">
         <v>1</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -2391,18 +2517,23 @@
       <c r="J26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K26" s="22" t="str">
+      <c r="K26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L26" s="24"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N26" s="26"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
+      <c r="A27" s="18"/>
       <c r="B27" s="5">
         <v>7</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="1">
         <v>1</v>
       </c>
       <c r="D27" s="5" t="s">
@@ -2426,18 +2557,23 @@
       <c r="J27" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K27" s="22" t="str">
+      <c r="K27" s="1" t="str">
         <f>REPT(IF(I27="Yes",1,0),C27)</f>
         <v>1</v>
       </c>
-      <c r="L27" s="24"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="26"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
+      <c r="A28" s="18"/>
       <c r="B28" s="5">
         <v>6</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="1">
         <v>1</v>
       </c>
       <c r="D28" s="5" t="s">
@@ -2461,18 +2597,23 @@
       <c r="J28" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="22" t="str">
+      <c r="K28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L28" s="24"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="26"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
+      <c r="A29" s="18"/>
       <c r="B29" s="5">
         <v>5</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="1">
         <v>1</v>
       </c>
       <c r="D29" s="5" t="s">
@@ -2496,18 +2637,23 @@
       <c r="J29" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="22" t="str">
+      <c r="K29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L29" s="24"/>
+      <c r="L29" s="19"/>
+      <c r="M29" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N29" s="26"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
+      <c r="A30" s="18"/>
       <c r="B30" s="5">
         <v>4</v>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="1">
         <v>1</v>
       </c>
       <c r="D30" s="5"/>
@@ -2525,18 +2671,23 @@
         <v>139</v>
       </c>
       <c r="J30" s="9"/>
-      <c r="K30" s="22" t="str">
+      <c r="K30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L30" s="24"/>
+      <c r="L30" s="19"/>
+      <c r="M30" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="26"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
+      <c r="A31" s="18"/>
       <c r="B31" s="5">
         <v>3</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="1">
         <v>1</v>
       </c>
       <c r="D31" s="5" t="s">
@@ -2560,18 +2711,23 @@
       <c r="J31" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="K31" s="22" t="str">
+      <c r="K31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L31" s="24"/>
+      <c r="L31" s="19"/>
+      <c r="M31" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N31" s="26"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="16"/>
+      <c r="A32" s="18"/>
       <c r="B32" s="5">
         <v>2</v>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="1">
         <v>1</v>
       </c>
       <c r="D32" s="5"/>
@@ -2589,18 +2745,23 @@
         <v>139</v>
       </c>
       <c r="J32" s="9"/>
-      <c r="K32" s="22" t="str">
+      <c r="K32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L32" s="24"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
+      <c r="L32" s="19"/>
+      <c r="M32" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N32" s="26"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" s="18"/>
       <c r="B33" s="5">
         <v>1</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="1">
         <v>1</v>
       </c>
       <c r="D33" s="5" t="s">
@@ -2624,18 +2785,23 @@
       <c r="J33" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K33" s="22" t="str">
+      <c r="K33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L33" s="24"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N33" s="26"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A34" s="18"/>
       <c r="B34" s="5">
         <v>0</v>
       </c>
-      <c r="C34" s="22">
+      <c r="C34" s="1">
         <v>1</v>
       </c>
       <c r="D34" s="5"/>
@@ -2653,52 +2819,57 @@
         <v>139</v>
       </c>
       <c r="J34" s="9"/>
-      <c r="K34" s="22" t="str">
+      <c r="K34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L34" s="24"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L34" s="19"/>
+      <c r="M34" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N34" s="27"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="12"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="12"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="12"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="12"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="12"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
@@ -2717,11 +2888,12 @@
       <c r="A53" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A3:A11"/>
     <mergeCell ref="A12:A34"/>
     <mergeCell ref="L3:L11"/>
     <mergeCell ref="L12:L34"/>
+    <mergeCell ref="N12:N34"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="B3:I34">
@@ -3047,7 +3219,7 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="19" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -3062,7 +3234,7 @@
       <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="20" t="s">
         <v>207</v>
       </c>
       <c r="I7" s="7" t="s">
@@ -3079,7 +3251,7 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
+      <c r="A8" s="19"/>
       <c r="B8" s="7" t="s">
         <v>176</v>
       </c>
@@ -3092,7 +3264,7 @@
       <c r="E8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="19"/>
+      <c r="H8" s="21"/>
       <c r="I8" s="7" t="s">
         <v>187</v>
       </c>
@@ -3107,7 +3279,7 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="1">
         <v>13</v>
       </c>
@@ -3118,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="20" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
@@ -3135,7 +3307,7 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+      <c r="A10" s="19"/>
       <c r="B10" s="7">
         <v>12</v>
       </c>
@@ -3148,7 +3320,7 @@
       <c r="E10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="20"/>
+      <c r="H10" s="22"/>
       <c r="I10" s="7" t="s">
         <v>189</v>
       </c>
@@ -3163,7 +3335,7 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="1">
         <v>11</v>
       </c>
@@ -3174,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="H11" s="20"/>
+      <c r="H11" s="22"/>
       <c r="I11" s="1">
         <v>19</v>
       </c>
@@ -3189,7 +3361,7 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
+      <c r="A12" s="19"/>
       <c r="B12" s="7">
         <v>10</v>
       </c>
@@ -3202,7 +3374,7 @@
       <c r="E12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="22"/>
       <c r="I12" s="1">
         <v>18</v>
       </c>
@@ -3215,7 +3387,7 @@
       <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -3226,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="H13" s="20"/>
+      <c r="H13" s="22"/>
       <c r="I13" s="7">
         <v>17</v>
       </c>
@@ -3239,7 +3411,7 @@
       <c r="L13" s="7"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="7">
         <v>8</v>
       </c>
@@ -3252,7 +3424,7 @@
       <c r="E14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="20"/>
+      <c r="H14" s="22"/>
       <c r="I14" s="1">
         <v>16</v>
       </c>
@@ -3265,7 +3437,7 @@
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="1">
         <v>7</v>
       </c>
@@ -3276,7 +3448,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="1"/>
-      <c r="H15" s="20"/>
+      <c r="H15" s="22"/>
       <c r="I15" s="1">
         <v>15</v>
       </c>
@@ -3289,7 +3461,7 @@
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="7">
         <v>6</v>
       </c>
@@ -3302,7 +3474,7 @@
       <c r="E16" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="20"/>
+      <c r="H16" s="22"/>
       <c r="I16" s="7">
         <v>14</v>
       </c>
@@ -3315,7 +3487,7 @@
       <c r="L16" s="7"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="1">
         <v>5</v>
       </c>
@@ -3326,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1"/>
-      <c r="H17" s="20"/>
+      <c r="H17" s="22"/>
       <c r="I17" s="1">
         <v>13</v>
       </c>
@@ -3339,7 +3511,7 @@
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="7">
         <v>4</v>
       </c>
@@ -3352,7 +3524,7 @@
       <c r="E18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="20"/>
+      <c r="H18" s="22"/>
       <c r="I18" s="1">
         <v>12</v>
       </c>
@@ -3365,7 +3537,7 @@
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="1">
         <v>3</v>
       </c>
@@ -3376,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1"/>
-      <c r="H19" s="20"/>
+      <c r="H19" s="22"/>
       <c r="I19" s="1">
         <v>11</v>
       </c>
@@ -3389,7 +3561,7 @@
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="7">
         <v>2</v>
       </c>
@@ -3402,7 +3574,7 @@
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="20"/>
+      <c r="H20" s="22"/>
       <c r="I20" s="7">
         <v>10</v>
       </c>
@@ -3415,7 +3587,7 @@
       <c r="L20" s="7"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="1">
         <v>1</v>
       </c>
@@ -3426,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1"/>
-      <c r="H21" s="20"/>
+      <c r="H21" s="22"/>
       <c r="I21" s="1">
         <v>9</v>
       </c>
@@ -3439,7 +3611,7 @@
       <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="7">
         <v>0</v>
       </c>
@@ -3452,7 +3624,7 @@
       <c r="E22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="20"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="1">
         <v>8</v>
       </c>
@@ -3465,7 +3637,7 @@
       <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H23" s="20"/>
+      <c r="H23" s="22"/>
       <c r="I23" s="1">
         <v>7</v>
       </c>
@@ -3478,7 +3650,7 @@
       <c r="L23" s="1"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H24" s="20"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="1">
         <v>6</v>
       </c>
@@ -3491,7 +3663,7 @@
       <c r="L24" s="1"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H25" s="20"/>
+      <c r="H25" s="22"/>
       <c r="I25" s="1">
         <v>5</v>
       </c>
@@ -3504,7 +3676,7 @@
       <c r="L25" s="1"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H26" s="20"/>
+      <c r="H26" s="22"/>
       <c r="I26" s="1">
         <v>4</v>
       </c>
@@ -3517,7 +3689,7 @@
       <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H27" s="20"/>
+      <c r="H27" s="22"/>
       <c r="I27" s="1">
         <v>3</v>
       </c>
@@ -3530,7 +3702,7 @@
       <c r="L27" s="1"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H28" s="20"/>
+      <c r="H28" s="22"/>
       <c r="I28" s="1">
         <v>2</v>
       </c>
@@ -3543,7 +3715,7 @@
       <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H29" s="20"/>
+      <c r="H29" s="22"/>
       <c r="I29" s="1">
         <v>1</v>
       </c>
@@ -3556,7 +3728,7 @@
       <c r="L29" s="1"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H30" s="19"/>
+      <c r="H30" s="21"/>
       <c r="I30" s="1">
         <v>0</v>
       </c>

--- a/riscv-csr.xlsx
+++ b/riscv-csr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\hd\riscv-simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CBAB5EA-141A-4DFE-9315-FE23E921BD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8B1451-E970-4672-9E00-9D3A033B451E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="464" activeTab="1" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="464" activeTab="2" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR Table" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="216">
   <si>
     <t>misa</t>
   </si>
@@ -713,9 +713,6 @@
     <t>medelegh</t>
   </si>
   <si>
-    <t>Writeable</t>
-  </si>
-  <si>
     <t>Default Value</t>
   </si>
   <si>
@@ -735,6 +732,9 @@
   </si>
   <si>
     <t>Implementation Mask sstatus joined</t>
+  </si>
+  <si>
+    <t>Delegateable</t>
   </si>
 </sst>
 </file>
@@ -863,7 +863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -907,6 +907,9 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -925,25 +928,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1562,7 +1553,7 @@
         <v>50</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>51</v>
@@ -1583,23 +1574,23 @@
         <v>67</v>
       </c>
       <c r="J2" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="K2" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="K2" s="13" t="s">
-        <v>211</v>
-      </c>
       <c r="L2" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -1627,17 +1618,17 @@
         <f>REPT(IF(I3="Yes",1,0),C3)</f>
         <v>000000000000000000000</v>
       </c>
-      <c r="L3" s="19" t="str" cm="1">
+      <c r="L3" s="20" t="str" cm="1">
         <f t="array" ref="L3">bin2hex_32(_xlfn.CONCAT(K3:K11))</f>
         <v>00000000</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N3" s="24"/>
+      <c r="N3" s="15"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="5">
         <v>10</v>
       </c>
@@ -1667,14 +1658,14 @@
         <f t="shared" ref="K4:K34" si="0">REPT(IF(I4="Yes",1,0),C4)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="19"/>
+      <c r="L4" s="20"/>
       <c r="M4" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N4" s="24"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5">
         <v>9</v>
       </c>
@@ -1704,14 +1695,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L5" s="19"/>
+      <c r="L5" s="20"/>
       <c r="M5" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N5" s="24"/>
+      <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
+      <c r="A6" s="17"/>
       <c r="B6" s="5">
         <v>8</v>
       </c>
@@ -1737,14 +1728,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="19"/>
+      <c r="L6" s="20"/>
       <c r="M6" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N6" s="24"/>
+      <c r="N6" s="15"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5">
         <v>7</v>
       </c>
@@ -1774,14 +1765,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="19"/>
+      <c r="L7" s="20"/>
       <c r="M7" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N7" s="24"/>
+      <c r="N7" s="15"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="5">
         <v>6</v>
       </c>
@@ -1811,14 +1802,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L8" s="19"/>
+      <c r="L8" s="20"/>
       <c r="M8" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N8" s="24"/>
+      <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="16"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1848,15 +1839,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L9" s="19"/>
+      <c r="L9" s="20"/>
       <c r="M9" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N9" s="24"/>
+      <c r="N9" s="15"/>
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="5">
         <v>4</v>
       </c>
@@ -1886,14 +1877,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="19"/>
+      <c r="L10" s="20"/>
       <c r="M10" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N10" s="24"/>
+      <c r="N10" s="15"/>
     </row>
     <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
+      <c r="A11" s="18"/>
       <c r="B11" s="5" t="s">
         <v>53</v>
       </c>
@@ -1919,15 +1910,15 @@
         <f t="shared" si="0"/>
         <v>0000</v>
       </c>
-      <c r="L11" s="19"/>
+      <c r="L11" s="20"/>
       <c r="M11" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="N11" s="24"/>
+      <c r="N11" s="15"/>
       <c r="O11" s="14"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="5">
@@ -1961,21 +1952,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="19" t="str" cm="1">
+      <c r="L12" s="20" t="str" cm="1">
         <f t="array" ref="L12">bin2hex_32(_xlfn.CONCAT(K12:K34))</f>
         <v>007E19AA</v>
       </c>
-      <c r="M12" s="23" t="str">
+      <c r="M12" s="1" t="str">
         <f>REPT(IF(AND(J12="Yes",I12="Yes"),1,0),C12)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="25" t="str" cm="1">
+      <c r="N12" s="21" t="str" cm="1">
         <f t="array" ref="N12">bin2hex_32(_xlfn.CONCAT(M12:M34))</f>
         <v>000C0122</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
+      <c r="A13" s="19"/>
       <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
@@ -2001,15 +1992,15 @@
         <f t="shared" si="0"/>
         <v>000000</v>
       </c>
-      <c r="L13" s="19"/>
-      <c r="M13" s="23" t="str">
+      <c r="L13" s="20"/>
+      <c r="M13" s="1" t="str">
         <f t="shared" ref="M13:M34" si="1">REPT(IF(AND(J13="Yes",I13="Yes"),1,0),C13)</f>
         <v>000000</v>
       </c>
-      <c r="N13" s="26"/>
+      <c r="N13" s="22"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="5">
         <v>24</v>
       </c>
@@ -2041,15 +2032,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="19"/>
-      <c r="M14" s="23" t="str">
+      <c r="L14" s="20"/>
+      <c r="M14" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N14" s="26"/>
+      <c r="N14" s="22"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
+      <c r="A15" s="19"/>
       <c r="B15" s="5">
         <v>23</v>
       </c>
@@ -2081,15 +2072,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L15" s="19"/>
-      <c r="M15" s="23" t="str">
+      <c r="L15" s="20"/>
+      <c r="M15" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N15" s="26"/>
+      <c r="N15" s="22"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
+      <c r="A16" s="19"/>
       <c r="B16" s="5">
         <v>22</v>
       </c>
@@ -2121,15 +2112,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L16" s="19"/>
-      <c r="M16" s="23" t="str">
+      <c r="L16" s="20"/>
+      <c r="M16" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N16" s="26"/>
+      <c r="N16" s="22"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
+      <c r="A17" s="19"/>
       <c r="B17" s="5">
         <v>21</v>
       </c>
@@ -2161,15 +2152,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L17" s="19"/>
-      <c r="M17" s="23" t="str">
+      <c r="L17" s="20"/>
+      <c r="M17" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N17" s="26"/>
+      <c r="N17" s="22"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
+      <c r="A18" s="19"/>
       <c r="B18" s="5">
         <v>20</v>
       </c>
@@ -2201,15 +2192,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L18" s="19"/>
-      <c r="M18" s="23" t="str">
+      <c r="L18" s="20"/>
+      <c r="M18" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="26"/>
+      <c r="N18" s="22"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="5">
         <v>19</v>
       </c>
@@ -2241,15 +2232,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L19" s="19"/>
-      <c r="M19" s="23" t="str">
+      <c r="L19" s="20"/>
+      <c r="M19" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N19" s="26"/>
+      <c r="N19" s="22"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="5">
         <v>18</v>
       </c>
@@ -2281,15 +2272,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L20" s="19"/>
-      <c r="M20" s="23" t="str">
+      <c r="L20" s="20"/>
+      <c r="M20" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N20" s="26"/>
+      <c r="N20" s="22"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="5">
         <v>17</v>
       </c>
@@ -2321,15 +2312,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L21" s="19"/>
-      <c r="M21" s="23" t="str">
+      <c r="L21" s="20"/>
+      <c r="M21" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N21" s="26"/>
+      <c r="N21" s="22"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="5" t="s">
         <v>47</v>
       </c>
@@ -2361,15 +2352,15 @@
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L22" s="19"/>
-      <c r="M22" s="23" t="str">
+      <c r="L22" s="20"/>
+      <c r="M22" s="1" t="str">
         <f t="shared" si="1"/>
         <v>00</v>
       </c>
-      <c r="N22" s="26"/>
+      <c r="N22" s="22"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="5" t="s">
         <v>48</v>
       </c>
@@ -2401,15 +2392,15 @@
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L23" s="19"/>
-      <c r="M23" s="23" t="str">
+      <c r="L23" s="20"/>
+      <c r="M23" s="1" t="str">
         <f t="shared" si="1"/>
         <v>00</v>
       </c>
-      <c r="N23" s="26"/>
+      <c r="N23" s="22"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="5" t="s">
         <v>49</v>
       </c>
@@ -2441,15 +2432,15 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="L24" s="19"/>
-      <c r="M24" s="23" t="str">
+      <c r="L24" s="20"/>
+      <c r="M24" s="1" t="str">
         <f t="shared" si="1"/>
         <v>00</v>
       </c>
-      <c r="N24" s="26"/>
+      <c r="N24" s="22"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="5" t="s">
         <v>138</v>
       </c>
@@ -2481,15 +2472,15 @@
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L25" s="19"/>
-      <c r="M25" s="23" t="str">
+      <c r="L25" s="20"/>
+      <c r="M25" s="1" t="str">
         <f t="shared" si="1"/>
         <v>00</v>
       </c>
-      <c r="N25" s="26"/>
+      <c r="N25" s="22"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="5">
         <v>8</v>
       </c>
@@ -2521,15 +2512,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L26" s="19"/>
-      <c r="M26" s="23" t="str">
+      <c r="L26" s="20"/>
+      <c r="M26" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N26" s="26"/>
+      <c r="N26" s="22"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="5">
         <v>7</v>
       </c>
@@ -2561,15 +2552,15 @@
         <f>REPT(IF(I27="Yes",1,0),C27)</f>
         <v>1</v>
       </c>
-      <c r="L27" s="19"/>
-      <c r="M27" s="23" t="str">
+      <c r="L27" s="20"/>
+      <c r="M27" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N27" s="26"/>
+      <c r="N27" s="22"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="5">
         <v>6</v>
       </c>
@@ -2601,15 +2592,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L28" s="19"/>
-      <c r="M28" s="23" t="str">
+      <c r="L28" s="20"/>
+      <c r="M28" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="26"/>
+      <c r="N28" s="22"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="5">
         <v>5</v>
       </c>
@@ -2641,15 +2632,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L29" s="19"/>
-      <c r="M29" s="23" t="str">
+      <c r="L29" s="20"/>
+      <c r="M29" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N29" s="26"/>
+      <c r="N29" s="22"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
+      <c r="A30" s="19"/>
       <c r="B30" s="5">
         <v>4</v>
       </c>
@@ -2675,15 +2666,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L30" s="19"/>
-      <c r="M30" s="23" t="str">
+      <c r="L30" s="20"/>
+      <c r="M30" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N30" s="26"/>
+      <c r="N30" s="22"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
+      <c r="A31" s="19"/>
       <c r="B31" s="5">
         <v>3</v>
       </c>
@@ -2715,15 +2706,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L31" s="19"/>
-      <c r="M31" s="23" t="str">
+      <c r="L31" s="20"/>
+      <c r="M31" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N31" s="26"/>
+      <c r="N31" s="22"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
+      <c r="A32" s="19"/>
       <c r="B32" s="5">
         <v>2</v>
       </c>
@@ -2749,15 +2740,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L32" s="19"/>
-      <c r="M32" s="23" t="str">
+      <c r="L32" s="20"/>
+      <c r="M32" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N32" s="26"/>
+      <c r="N32" s="22"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
+      <c r="A33" s="19"/>
       <c r="B33" s="5">
         <v>1</v>
       </c>
@@ -2789,15 +2780,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L33" s="19"/>
-      <c r="M33" s="23" t="str">
+      <c r="L33" s="20"/>
+      <c r="M33" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N33" s="26"/>
+      <c r="N33" s="22"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
+      <c r="A34" s="19"/>
       <c r="B34" s="5">
         <v>0</v>
       </c>
@@ -2823,12 +2814,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L34" s="19"/>
-      <c r="M34" s="23" t="str">
+      <c r="L34" s="20"/>
+      <c r="M34" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N34" s="27"/>
+      <c r="N34" s="23"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
@@ -2924,7 +2915,8 @@
     <col min="5" max="5" width="11.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38.28515625" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="6"/>
+    <col min="8" max="8" width="15.7109375" style="6" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3174,24 +3166,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400D1ED3-44A7-49E9-A961-E022D71E5837}">
-  <dimension ref="A6:L30"/>
+  <dimension ref="A6:M30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="2"/>
     <col min="3" max="3" width="33.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="4" max="5" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.28515625" style="2" customWidth="1"/>
     <col min="8" max="8" width="18.5703125" style="2" customWidth="1"/>
     <col min="9" max="9" width="7.7109375" style="2" customWidth="1"/>
     <col min="10" max="10" width="29.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="2"/>
+    <col min="11" max="12" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:12" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>50</v>
       </c>
@@ -3199,10 +3190,13 @@
         <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>208</v>
+        <v>67</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="H6" s="8"/>
       <c r="I6" s="1" t="s">
@@ -3212,14 +3206,17 @@
         <v>51</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -3231,10 +3228,9 @@
       <c r="D7" s="7">
         <v>0</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="20" t="s">
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="H7" s="21" t="s">
         <v>207</v>
       </c>
       <c r="I7" s="7" t="s">
@@ -3246,12 +3242,11 @@
       <c r="K7" s="7">
         <v>0</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="19"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
       <c r="B8" s="7" t="s">
         <v>176</v>
       </c>
@@ -3261,10 +3256,9 @@
       <c r="D8" s="7">
         <v>0</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="21"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="H8" s="23"/>
       <c r="I8" s="7" t="s">
         <v>187</v>
       </c>
@@ -3274,23 +3268,27 @@
       <c r="K8" s="7">
         <v>0</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="20"/>
+      <c r="B9" s="24">
+        <v>13</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="24">
+        <v>0</v>
+      </c>
+      <c r="E9" s="24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
-      <c r="B9" s="1">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="H9" s="20" t="s">
+      <c r="F9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="21" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
@@ -3302,12 +3300,11 @@
       <c r="K9" s="7">
         <v>0</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="20"/>
       <c r="B10" s="7">
         <v>12</v>
       </c>
@@ -3317,9 +3314,8 @@
       <c r="D10" s="7">
         <v>0</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="H10" s="22"/>
       <c r="I10" s="7" t="s">
         <v>189</v>
@@ -3330,38 +3326,45 @@
       <c r="K10" s="7">
         <v>0</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="20"/>
+      <c r="B11" s="4">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="1">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1"/>
       <c r="H11" s="22"/>
-      <c r="I11" s="1">
+      <c r="I11" s="24">
         <v>19</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J11" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1" t="s">
+      <c r="K11" s="24">
+        <v>0</v>
+      </c>
+      <c r="L11" s="24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
+      <c r="M11" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
       <c r="B12" s="7">
         <v>10</v>
       </c>
@@ -3371,33 +3374,40 @@
       <c r="D12" s="7">
         <v>0</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="24">
+        <v>18</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="K12" s="24">
+        <v>0</v>
+      </c>
+      <c r="L12" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="1">
-        <v>18</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="1">
+      <c r="M12" s="24"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="4">
         <v>9</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="1">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1"/>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="H13" s="22"/>
       <c r="I13" s="7">
         <v>17</v>
@@ -3409,9 +3419,10 @@
         <v>0</v>
       </c>
       <c r="L13" s="7"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
       <c r="B14" s="7">
         <v>8</v>
       </c>
@@ -3421,47 +3432,61 @@
       <c r="D14" s="7">
         <v>0</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="24">
+        <v>16</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="K14" s="24">
+        <v>0</v>
+      </c>
+      <c r="L14" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="1">
-        <v>16</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
-      <c r="B15" s="1">
+      <c r="M14" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="4">
         <v>7</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1"/>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>23</v>
+      </c>
       <c r="H15" s="22"/>
-      <c r="I15" s="1">
+      <c r="I15" s="4">
         <v>15</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="J15" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="K15" s="1">
-        <v>0</v>
-      </c>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
+      <c r="K15" s="4">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
       <c r="B16" s="7">
         <v>6</v>
       </c>
@@ -3471,9 +3496,8 @@
       <c r="D16" s="7">
         <v>0</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
       <c r="H16" s="22"/>
       <c r="I16" s="7">
         <v>14</v>
@@ -3485,33 +3509,44 @@
         <v>0</v>
       </c>
       <c r="L16" s="7"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="1">
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="4">
         <v>5</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1"/>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="H17" s="22"/>
-      <c r="I17" s="1">
+      <c r="I17" s="4">
         <v>13</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-      <c r="L17" s="1"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
+      <c r="K17" s="4">
+        <v>0</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
       <c r="B18" s="7">
         <v>4</v>
       </c>
@@ -3521,47 +3556,61 @@
       <c r="D18" s="7">
         <v>0</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="4">
+        <v>12</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" s="4">
+        <v>0</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="4">
+        <v>3</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="1">
-        <v>12</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="1">
-        <v>3</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D19" s="1">
-        <v>0</v>
-      </c>
-      <c r="E19" s="1"/>
       <c r="H19" s="22"/>
-      <c r="I19" s="1">
+      <c r="I19" s="4">
         <v>11</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="J19" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-      <c r="L19" s="1"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
+      <c r="K19" s="4">
+        <v>0</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
       <c r="B20" s="7">
         <v>2</v>
       </c>
@@ -3571,9 +3620,8 @@
       <c r="D20" s="7">
         <v>0</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
       <c r="H20" s="22"/>
       <c r="I20" s="7">
         <v>10</v>
@@ -3585,33 +3633,44 @@
         <v>0</v>
       </c>
       <c r="L20" s="7"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1" t="s">
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="4">
+        <v>1</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D21" s="1">
-        <v>0</v>
-      </c>
-      <c r="E21" s="1"/>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="H21" s="22"/>
-      <c r="I21" s="1">
+      <c r="I21" s="4">
         <v>9</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-      <c r="L21" s="1"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="K21" s="4">
+        <v>0</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
       <c r="B22" s="7">
         <v>0</v>
       </c>
@@ -3621,124 +3680,168 @@
       <c r="D22" s="7">
         <v>0</v>
       </c>
-      <c r="E22" s="7" t="s">
-        <v>23</v>
-      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
       <c r="H22" s="22"/>
-      <c r="I22" s="1">
+      <c r="I22" s="4">
         <v>8</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-      <c r="L22" s="1"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K22" s="4">
+        <v>0</v>
+      </c>
+      <c r="L22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H23" s="22"/>
-      <c r="I23" s="1">
+      <c r="I23" s="4">
         <v>7</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="J23" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K23" s="4">
+        <v>0</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H24" s="22"/>
-      <c r="I24" s="1">
+      <c r="I24" s="4">
         <v>6</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K24" s="4">
+        <v>0</v>
+      </c>
+      <c r="L24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H25" s="22"/>
-      <c r="I25" s="1">
+      <c r="I25" s="4">
         <v>5</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="J25" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K25" s="4">
+        <v>0</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H26" s="22"/>
-      <c r="I26" s="1">
+      <c r="I26" s="4">
         <v>4</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="J26" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K26" s="4">
+        <v>0</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H27" s="22"/>
-      <c r="I27" s="1">
+      <c r="I27" s="4">
         <v>3</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="J27" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K27" s="4">
+        <v>0</v>
+      </c>
+      <c r="L27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H28" s="22"/>
-      <c r="I28" s="1">
+      <c r="I28" s="4">
         <v>2</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K28" s="4">
+        <v>0</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="H29" s="22"/>
-      <c r="I29" s="1">
-        <v>1</v>
-      </c>
-      <c r="J29" s="1" t="s">
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H30" s="21"/>
-      <c r="I30" s="1">
-        <v>0</v>
-      </c>
-      <c r="J30" s="1" t="s">
+      <c r="K29" s="4">
+        <v>0</v>
+      </c>
+      <c r="L29" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H30" s="23"/>
+      <c r="I30" s="4">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1"/>
+      <c r="K30" s="4">
+        <v>0</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/riscv-csr.xlsx
+++ b/riscv-csr.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\hd\riscv-simulator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\archlinux\home\hd\Desktop\work-github\riscv-simulator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8B1451-E970-4672-9E00-9D3A033B451E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3797E01-FAC9-43DA-AD64-DEABBE4A1617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="464" activeTab="2" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="464" activeTab="3" xr2:uid="{8293AE58-3985-422E-ACBE-0DE584F3F72C}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR Table" sheetId="1" r:id="rId1"/>
     <sheet name="mstatus mstatush sstatus" sheetId="2" r:id="rId2"/>
     <sheet name="mip mie" sheetId="5" r:id="rId3"/>
-    <sheet name="mideleg medeleg medelegh" sheetId="6" r:id="rId4"/>
+    <sheet name="misa" sheetId="7" r:id="rId4"/>
+    <sheet name="mideleg medeleg medelegh" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="bin2hex_32">_xlfn.LAMBDA(_xlpm.bin_str,    _xlfn.LET(     _xlpm.padded, RIGHT(REPT("0", 32) &amp; _xlpm.bin_str, 32),     _xlfn.CONCAT(       BIN2HEX(MID(_xlpm.padded, 1, 8), 2),       BIN2HEX(MID(_xlpm.padded, 9, 8), 2),       BIN2HEX(MID(_xlpm.padded, 17, 8), 2),       BIN2HEX(MID(_xlpm.padded, 25, 8), 2)     )   ) )</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="246">
   <si>
     <t>misa</t>
   </si>
@@ -735,6 +736,96 @@
   </si>
   <si>
     <t>Delegateable</t>
+  </si>
+  <si>
+    <t>MXL</t>
+  </si>
+  <si>
+    <t>Writeable</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>01</t>
   </si>
 </sst>
 </file>
@@ -767,7 +858,7 @@
       <name val="Consolas"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -795,6 +886,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -863,7 +960,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -910,6 +1007,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -934,7 +1034,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1590,7 +1711,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -1618,7 +1739,7 @@
         <f>REPT(IF(I3="Yes",1,0),C3)</f>
         <v>000000000000000000000</v>
       </c>
-      <c r="L3" s="20" t="str" cm="1">
+      <c r="L3" s="21" t="str" cm="1">
         <f t="array" ref="L3">bin2hex_32(_xlfn.CONCAT(K3:K11))</f>
         <v>00000000</v>
       </c>
@@ -1628,7 +1749,7 @@
       <c r="N3" s="15"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="5">
         <v>10</v>
       </c>
@@ -1658,14 +1779,14 @@
         <f t="shared" ref="K4:K34" si="0">REPT(IF(I4="Yes",1,0),C4)</f>
         <v>0</v>
       </c>
-      <c r="L4" s="20"/>
+      <c r="L4" s="21"/>
       <c r="M4" s="5" t="s">
         <v>139</v>
       </c>
       <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="5">
         <v>9</v>
       </c>
@@ -1695,14 +1816,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L5" s="20"/>
+      <c r="L5" s="21"/>
       <c r="M5" s="5" t="s">
         <v>139</v>
       </c>
       <c r="N5" s="15"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+      <c r="A6" s="18"/>
       <c r="B6" s="5">
         <v>8</v>
       </c>
@@ -1728,14 +1849,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L6" s="20"/>
+      <c r="L6" s="21"/>
       <c r="M6" s="5" t="s">
         <v>139</v>
       </c>
       <c r="N6" s="15"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
+      <c r="A7" s="18"/>
       <c r="B7" s="5">
         <v>7</v>
       </c>
@@ -1765,14 +1886,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="20"/>
+      <c r="L7" s="21"/>
       <c r="M7" s="5" t="s">
         <v>139</v>
       </c>
       <c r="N7" s="15"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
+      <c r="A8" s="18"/>
       <c r="B8" s="5">
         <v>6</v>
       </c>
@@ -1802,14 +1923,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L8" s="20"/>
+      <c r="L8" s="21"/>
       <c r="M8" s="5" t="s">
         <v>139</v>
       </c>
       <c r="N8" s="15"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+      <c r="A9" s="18"/>
       <c r="B9" s="5">
         <v>5</v>
       </c>
@@ -1839,7 +1960,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L9" s="20"/>
+      <c r="L9" s="21"/>
       <c r="M9" s="5" t="s">
         <v>139</v>
       </c>
@@ -1847,7 +1968,7 @@
       <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+      <c r="A10" s="18"/>
       <c r="B10" s="5">
         <v>4</v>
       </c>
@@ -1877,14 +1998,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="20"/>
+      <c r="L10" s="21"/>
       <c r="M10" s="5" t="s">
         <v>139</v>
       </c>
       <c r="N10" s="15"/>
     </row>
     <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+      <c r="A11" s="19"/>
       <c r="B11" s="5" t="s">
         <v>53</v>
       </c>
@@ -1910,7 +2031,7 @@
         <f t="shared" si="0"/>
         <v>0000</v>
       </c>
-      <c r="L11" s="20"/>
+      <c r="L11" s="21"/>
       <c r="M11" s="5" t="s">
         <v>139</v>
       </c>
@@ -1918,7 +2039,7 @@
       <c r="O11" s="14"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="20" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="5">
@@ -1952,7 +2073,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="20" t="str" cm="1">
+      <c r="L12" s="21" t="str" cm="1">
         <f t="array" ref="L12">bin2hex_32(_xlfn.CONCAT(K12:K34))</f>
         <v>007E19AA</v>
       </c>
@@ -1960,13 +2081,13 @@
         <f>REPT(IF(AND(J12="Yes",I12="Yes"),1,0),C12)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="21" t="str" cm="1">
+      <c r="N12" s="22" t="str" cm="1">
         <f t="array" ref="N12">bin2hex_32(_xlfn.CONCAT(M12:M34))</f>
         <v>000C0122</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
@@ -1992,15 +2113,15 @@
         <f t="shared" si="0"/>
         <v>000000</v>
       </c>
-      <c r="L13" s="20"/>
+      <c r="L13" s="21"/>
       <c r="M13" s="1" t="str">
         <f t="shared" ref="M13:M34" si="1">REPT(IF(AND(J13="Yes",I13="Yes"),1,0),C13)</f>
         <v>000000</v>
       </c>
-      <c r="N13" s="22"/>
+      <c r="N13" s="23"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="5">
         <v>24</v>
       </c>
@@ -2032,15 +2153,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L14" s="20"/>
+      <c r="L14" s="21"/>
       <c r="M14" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N14" s="22"/>
+      <c r="N14" s="23"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
+      <c r="A15" s="20"/>
       <c r="B15" s="5">
         <v>23</v>
       </c>
@@ -2072,15 +2193,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L15" s="20"/>
+      <c r="L15" s="21"/>
       <c r="M15" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N15" s="22"/>
+      <c r="N15" s="23"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
+      <c r="A16" s="20"/>
       <c r="B16" s="5">
         <v>22</v>
       </c>
@@ -2112,15 +2233,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L16" s="20"/>
+      <c r="L16" s="21"/>
       <c r="M16" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N16" s="22"/>
+      <c r="N16" s="23"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
+      <c r="A17" s="20"/>
       <c r="B17" s="5">
         <v>21</v>
       </c>
@@ -2152,15 +2273,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L17" s="20"/>
+      <c r="L17" s="21"/>
       <c r="M17" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N17" s="22"/>
+      <c r="N17" s="23"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
+      <c r="A18" s="20"/>
       <c r="B18" s="5">
         <v>20</v>
       </c>
@@ -2192,15 +2313,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L18" s="20"/>
+      <c r="L18" s="21"/>
       <c r="M18" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N18" s="22"/>
+      <c r="N18" s="23"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
+      <c r="A19" s="20"/>
       <c r="B19" s="5">
         <v>19</v>
       </c>
@@ -2232,15 +2353,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L19" s="20"/>
+      <c r="L19" s="21"/>
       <c r="M19" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N19" s="22"/>
+      <c r="N19" s="23"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="5">
         <v>18</v>
       </c>
@@ -2272,15 +2393,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L20" s="20"/>
+      <c r="L20" s="21"/>
       <c r="M20" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N20" s="22"/>
+      <c r="N20" s="23"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="5">
         <v>17</v>
       </c>
@@ -2312,15 +2433,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L21" s="20"/>
+      <c r="L21" s="21"/>
       <c r="M21" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N21" s="22"/>
+      <c r="N21" s="23"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
+      <c r="A22" s="20"/>
       <c r="B22" s="5" t="s">
         <v>47</v>
       </c>
@@ -2352,15 +2473,15 @@
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L22" s="20"/>
+      <c r="L22" s="21"/>
       <c r="M22" s="1" t="str">
         <f t="shared" si="1"/>
         <v>00</v>
       </c>
-      <c r="N22" s="22"/>
+      <c r="N22" s="23"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
+      <c r="A23" s="20"/>
       <c r="B23" s="5" t="s">
         <v>48</v>
       </c>
@@ -2392,15 +2513,15 @@
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L23" s="20"/>
+      <c r="L23" s="21"/>
       <c r="M23" s="1" t="str">
         <f t="shared" si="1"/>
         <v>00</v>
       </c>
-      <c r="N23" s="22"/>
+      <c r="N23" s="23"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
+      <c r="A24" s="20"/>
       <c r="B24" s="5" t="s">
         <v>49</v>
       </c>
@@ -2432,15 +2553,15 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="L24" s="20"/>
+      <c r="L24" s="21"/>
       <c r="M24" s="1" t="str">
         <f t="shared" si="1"/>
         <v>00</v>
       </c>
-      <c r="N24" s="22"/>
+      <c r="N24" s="23"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
+      <c r="A25" s="20"/>
       <c r="B25" s="5" t="s">
         <v>138</v>
       </c>
@@ -2472,15 +2593,15 @@
         <f t="shared" si="0"/>
         <v>00</v>
       </c>
-      <c r="L25" s="20"/>
+      <c r="L25" s="21"/>
       <c r="M25" s="1" t="str">
         <f t="shared" si="1"/>
         <v>00</v>
       </c>
-      <c r="N25" s="22"/>
+      <c r="N25" s="23"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
+      <c r="A26" s="20"/>
       <c r="B26" s="5">
         <v>8</v>
       </c>
@@ -2512,15 +2633,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L26" s="20"/>
+      <c r="L26" s="21"/>
       <c r="M26" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N26" s="22"/>
+      <c r="N26" s="23"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="19"/>
+      <c r="A27" s="20"/>
       <c r="B27" s="5">
         <v>7</v>
       </c>
@@ -2552,15 +2673,15 @@
         <f>REPT(IF(I27="Yes",1,0),C27)</f>
         <v>1</v>
       </c>
-      <c r="L27" s="20"/>
+      <c r="L27" s="21"/>
       <c r="M27" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N27" s="22"/>
+      <c r="N27" s="23"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="19"/>
+      <c r="A28" s="20"/>
       <c r="B28" s="5">
         <v>6</v>
       </c>
@@ -2592,15 +2713,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L28" s="20"/>
+      <c r="L28" s="21"/>
       <c r="M28" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N28" s="22"/>
+      <c r="N28" s="23"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="19"/>
+      <c r="A29" s="20"/>
       <c r="B29" s="5">
         <v>5</v>
       </c>
@@ -2632,15 +2753,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L29" s="20"/>
+      <c r="L29" s="21"/>
       <c r="M29" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N29" s="22"/>
+      <c r="N29" s="23"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="19"/>
+      <c r="A30" s="20"/>
       <c r="B30" s="5">
         <v>4</v>
       </c>
@@ -2666,15 +2787,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L30" s="20"/>
+      <c r="L30" s="21"/>
       <c r="M30" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N30" s="22"/>
+      <c r="N30" s="23"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
+      <c r="A31" s="20"/>
       <c r="B31" s="5">
         <v>3</v>
       </c>
@@ -2706,15 +2827,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L31" s="20"/>
+      <c r="L31" s="21"/>
       <c r="M31" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N31" s="22"/>
+      <c r="N31" s="23"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
+      <c r="A32" s="20"/>
       <c r="B32" s="5">
         <v>2</v>
       </c>
@@ -2740,15 +2861,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L32" s="20"/>
+      <c r="L32" s="21"/>
       <c r="M32" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N32" s="22"/>
+      <c r="N32" s="23"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
+      <c r="A33" s="20"/>
       <c r="B33" s="5">
         <v>1</v>
       </c>
@@ -2780,15 +2901,15 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L33" s="20"/>
+      <c r="L33" s="21"/>
       <c r="M33" s="1" t="str">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N33" s="22"/>
+      <c r="N33" s="23"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
+      <c r="A34" s="20"/>
       <c r="B34" s="5">
         <v>0</v>
       </c>
@@ -2814,12 +2935,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L34" s="20"/>
+      <c r="L34" s="21"/>
       <c r="M34" s="1" t="str">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N34" s="23"/>
+      <c r="N34" s="24"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
@@ -3165,6 +3286,510 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE4BF47-6E7D-46DC-BEF8-68A92150F968}">
+  <dimension ref="G3:K35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="6" width="9.140625" style="6"/>
+    <col min="7" max="7" width="6.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="6"/>
+    <col min="9" max="9" width="13.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G4" s="10">
+        <v>31</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="32" t="str" cm="1">
+        <f t="array" ref="K4">bin2hex_32(_xlfn.CONCAT(I4:I35))</f>
+        <v>40141101</v>
+      </c>
+    </row>
+    <row r="5" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G5" s="10">
+        <v>30</v>
+      </c>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="32"/>
+    </row>
+    <row r="6" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G6" s="25">
+        <v>29</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="32"/>
+    </row>
+    <row r="7" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G7" s="25">
+        <v>28</v>
+      </c>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="32"/>
+    </row>
+    <row r="8" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G8" s="25">
+        <v>27</v>
+      </c>
+      <c r="H8" s="27"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="27"/>
+      <c r="K8" s="32"/>
+    </row>
+    <row r="9" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G9" s="25">
+        <v>26</v>
+      </c>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="32"/>
+    </row>
+    <row r="10" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G10" s="11">
+        <v>25</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="32"/>
+    </row>
+    <row r="11" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G11" s="11">
+        <v>24</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="32"/>
+    </row>
+    <row r="12" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G12" s="11">
+        <v>23</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="32"/>
+    </row>
+    <row r="13" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G13" s="11">
+        <v>22</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="32"/>
+    </row>
+    <row r="14" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G14" s="11">
+        <v>21</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="32"/>
+    </row>
+    <row r="15" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G15" s="10">
+        <v>20</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="32"/>
+    </row>
+    <row r="16" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G16" s="11">
+        <v>19</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="32"/>
+    </row>
+    <row r="17" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G17" s="10">
+        <v>18</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="32"/>
+    </row>
+    <row r="18" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G18" s="11">
+        <v>17</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="32"/>
+    </row>
+    <row r="19" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G19" s="11">
+        <v>16</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="32"/>
+    </row>
+    <row r="20" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G20" s="11">
+        <v>15</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="32"/>
+    </row>
+    <row r="21" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G21" s="11">
+        <v>14</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="32"/>
+    </row>
+    <row r="22" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G22" s="11">
+        <v>13</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="32"/>
+    </row>
+    <row r="23" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G23" s="10">
+        <v>12</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="32"/>
+    </row>
+    <row r="24" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G24" s="11">
+        <v>11</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="32"/>
+    </row>
+    <row r="25" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G25" s="11">
+        <v>10</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="32"/>
+    </row>
+    <row r="26" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G26" s="11">
+        <v>9</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="32"/>
+    </row>
+    <row r="27" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G27" s="10">
+        <v>8</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="32"/>
+    </row>
+    <row r="28" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G28" s="11">
+        <v>7</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="32"/>
+    </row>
+    <row r="29" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G29" s="11">
+        <v>6</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="32"/>
+    </row>
+    <row r="30" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G30" s="11">
+        <v>5</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="32"/>
+    </row>
+    <row r="31" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G31" s="11">
+        <v>4</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="32"/>
+    </row>
+    <row r="32" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G32" s="11">
+        <v>3</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="32"/>
+    </row>
+    <row r="33" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G33" s="11">
+        <v>2</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="32"/>
+    </row>
+    <row r="34" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G34" s="11">
+        <v>1</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="32"/>
+    </row>
+    <row r="35" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G35" s="10">
+        <v>0</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="K4:K35"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I6:I9"/>
+    <mergeCell ref="J6:J9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{400D1ED3-44A7-49E9-A961-E022D71E5837}">
   <dimension ref="A6:M30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
@@ -3216,7 +3841,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="21" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -3230,7 +3855,7 @@
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="22" t="s">
         <v>207</v>
       </c>
       <c r="I7" s="7" t="s">
@@ -3246,7 +3871,7 @@
       <c r="M7" s="7"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
+      <c r="A8" s="21"/>
       <c r="B8" s="7" t="s">
         <v>176</v>
       </c>
@@ -3258,7 +3883,7 @@
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
-      <c r="H8" s="23"/>
+      <c r="H8" s="24"/>
       <c r="I8" s="7" t="s">
         <v>187</v>
       </c>
@@ -3272,23 +3897,23 @@
       <c r="M8" s="7"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="24">
+      <c r="A9" s="21"/>
+      <c r="B9" s="16">
         <v>13</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="D9" s="24">
-        <v>0</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="21" t="s">
+      <c r="D9" s="16">
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="22" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
@@ -3304,7 +3929,7 @@
       <c r="M9" s="7"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="20"/>
+      <c r="A10" s="21"/>
       <c r="B10" s="7">
         <v>12</v>
       </c>
@@ -3316,7 +3941,7 @@
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="H10" s="22"/>
+      <c r="H10" s="23"/>
       <c r="I10" s="7" t="s">
         <v>189</v>
       </c>
@@ -3330,7 +3955,7 @@
       <c r="M10" s="7"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
+      <c r="A11" s="21"/>
       <c r="B11" s="4">
         <v>11</v>
       </c>
@@ -3343,28 +3968,28 @@
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="24">
+      <c r="F11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="23"/>
+      <c r="I11" s="16">
         <v>19</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="K11" s="24">
-        <v>0</v>
-      </c>
-      <c r="L11" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="24" t="s">
+      <c r="K11" s="16">
+        <v>0</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M11" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="7">
         <v>10</v>
       </c>
@@ -3376,23 +4001,23 @@
       </c>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="24">
+      <c r="H12" s="23"/>
+      <c r="I12" s="16">
         <v>18</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="K12" s="24">
-        <v>0</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="24"/>
+      <c r="K12" s="16">
+        <v>0</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M12" s="16"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="4">
         <v>9</v>
       </c>
@@ -3408,7 +4033,7 @@
       <c r="F13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="22"/>
+      <c r="H13" s="23"/>
       <c r="I13" s="7">
         <v>17</v>
       </c>
@@ -3422,7 +4047,7 @@
       <c r="M13" s="7"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="7">
         <v>8</v>
       </c>
@@ -3434,25 +4059,25 @@
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="24">
+      <c r="H14" s="23"/>
+      <c r="I14" s="16">
         <v>16</v>
       </c>
-      <c r="J14" s="24" t="s">
+      <c r="J14" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="K14" s="24">
-        <v>0</v>
-      </c>
-      <c r="L14" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" s="24" t="s">
+      <c r="K14" s="16">
+        <v>0</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="M14" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
+      <c r="A15" s="21"/>
       <c r="B15" s="4">
         <v>7</v>
       </c>
@@ -3465,10 +4090,10 @@
       <c r="E15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="22"/>
+      <c r="F15" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="23"/>
       <c r="I15" s="4">
         <v>15</v>
       </c>
@@ -3486,7 +4111,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
+      <c r="A16" s="21"/>
       <c r="B16" s="7">
         <v>6</v>
       </c>
@@ -3498,7 +4123,7 @@
       </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-      <c r="H16" s="22"/>
+      <c r="H16" s="23"/>
       <c r="I16" s="7">
         <v>14</v>
       </c>
@@ -3512,7 +4137,7 @@
       <c r="M16" s="7"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="4">
         <v>5</v>
       </c>
@@ -3528,7 +4153,7 @@
       <c r="F17" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="22"/>
+      <c r="H17" s="23"/>
       <c r="I17" s="4">
         <v>13</v>
       </c>
@@ -3546,7 +4171,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
+      <c r="A18" s="21"/>
       <c r="B18" s="7">
         <v>4</v>
       </c>
@@ -3558,7 +4183,7 @@
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
-      <c r="H18" s="22"/>
+      <c r="H18" s="23"/>
       <c r="I18" s="4">
         <v>12</v>
       </c>
@@ -3576,7 +4201,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="4">
         <v>3</v>
       </c>
@@ -3589,10 +4214,10 @@
       <c r="E19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="22"/>
+      <c r="F19" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="23"/>
       <c r="I19" s="4">
         <v>11</v>
       </c>
@@ -3605,12 +4230,12 @@
       <c r="L19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="24" t="s">
+      <c r="M19" s="16" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="7">
         <v>2</v>
       </c>
@@ -3622,7 +4247,7 @@
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
-      <c r="H20" s="22"/>
+      <c r="H20" s="23"/>
       <c r="I20" s="7">
         <v>10</v>
       </c>
@@ -3636,7 +4261,7 @@
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="20"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="4">
         <v>1</v>
       </c>
@@ -3652,7 +4277,7 @@
       <c r="F21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="22"/>
+      <c r="H21" s="23"/>
       <c r="I21" s="4">
         <v>9</v>
       </c>
@@ -3670,7 +4295,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="20"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="7">
         <v>0</v>
       </c>
@@ -3682,7 +4307,7 @@
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
-      <c r="H22" s="22"/>
+      <c r="H22" s="23"/>
       <c r="I22" s="4">
         <v>8</v>
       </c>
@@ -3700,7 +4325,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H23" s="22"/>
+      <c r="H23" s="23"/>
       <c r="I23" s="4">
         <v>7</v>
       </c>
@@ -3718,7 +4343,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H24" s="22"/>
+      <c r="H24" s="23"/>
       <c r="I24" s="4">
         <v>6</v>
       </c>
@@ -3736,7 +4361,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H25" s="22"/>
+      <c r="H25" s="23"/>
       <c r="I25" s="4">
         <v>5</v>
       </c>
@@ -3754,7 +4379,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H26" s="22"/>
+      <c r="H26" s="23"/>
       <c r="I26" s="4">
         <v>4</v>
       </c>
@@ -3772,7 +4397,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H27" s="22"/>
+      <c r="H27" s="23"/>
       <c r="I27" s="4">
         <v>3</v>
       </c>
@@ -3790,7 +4415,7 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H28" s="22"/>
+      <c r="H28" s="23"/>
       <c r="I28" s="4">
         <v>2</v>
       </c>
@@ -3808,7 +4433,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H29" s="22"/>
+      <c r="H29" s="23"/>
       <c r="I29" s="4">
         <v>1</v>
       </c>
@@ -3826,7 +4451,7 @@
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="H30" s="23"/>
+      <c r="H30" s="24"/>
       <c r="I30" s="4">
         <v>0</v>
       </c>
